--- a/2.data_processing/verbal_autopsy_recode_file.xlsx
+++ b/2.data_processing/verbal_autopsy_recode_file.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="7" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="8" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="study" sheetId="5" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3617" uniqueCount="1399">
   <si>
     <t>pos</t>
   </si>
@@ -4219,6 +4219,18 @@
   </si>
   <si>
     <t>Village Name</t>
+  </si>
+  <si>
+    <t>va_done</t>
+  </si>
+  <si>
+    <t>time_to_va</t>
+  </si>
+  <si>
+    <t>Verbal Autopsy Done</t>
+  </si>
+  <si>
+    <t>Number of Days from Death date taken to do Verbal Autopsy</t>
   </si>
 </sst>
 </file>
@@ -8174,7 +8186,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.90625" style="3" customWidth="1"/>
@@ -8807,7 +8819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -8815,10 +8827,10 @@
         <v>1203</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1348</v>
+        <v>1395</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1349</v>
+        <v>1397</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>14</v>
@@ -8848,7 +8860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="39" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -8856,10 +8868,10 @@
         <v>1203</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1172</v>
+        <v>1396</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>896</v>
+        <v>1398</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>14</v>
@@ -8889,18 +8901,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="26" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="10" t="s">
         <v>1203</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1131</v>
+        <v>1348</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1205</v>
+        <v>1349</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>14</v>
@@ -8930,8 +8942,90 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C19:D1048576 C1:D1">
+  <conditionalFormatting sqref="C21:D1048576 C1:D1">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
